--- a/data/input_params_range.xlsx
+++ b/data/input_params_range.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geo-checkout-user/Documents/2024_paleosol_PSM_CLP_case_study/paleosol_CLP/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geo-checkout-user/Documents/2024_paleosol_PSM_CLP_case_study/paleosol_CLP/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3D2BECF-E127-B549-B960-1637245176DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECDDB408-DF17-0846-92FF-41459A7EE762}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6520" yWindow="3200" windowWidth="28040" windowHeight="17440" xr2:uid="{C89A10F1-C584-8C4D-85A3-B57BD1FEEBA8}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="45">
   <si>
     <t>variable</t>
   </si>
@@ -162,6 +162,15 @@
   </si>
   <si>
     <t>fraction of non-growing season rainfall</t>
+  </si>
+  <si>
+    <t>temp_diff</t>
+  </si>
+  <si>
+    <t>difference between the annual mean regional surface temperature and global mean surface temperature</t>
+  </si>
+  <si>
+    <t>Clark et al., 2024; Lu et al., 2022</t>
   </si>
 </sst>
 </file>
@@ -197,7 +206,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -207,9 +216,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -545,16 +551,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66993087-6E19-A94F-947A-A00ACE4E99D5}">
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.83203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="24.83203125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.5" style="1" customWidth="1"/>
     <col min="5" max="5" width="8.83203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.83203125" style="4" customWidth="1"/>
-    <col min="7" max="7" width="10.83203125" style="4"/>
+    <col min="6" max="6" width="8.83203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10.83203125" style="1"/>
     <col min="8" max="8" width="35.33203125" style="3" customWidth="1"/>
     <col min="9" max="16384" width="10.83203125" style="3"/>
   </cols>
@@ -575,10 +581,10 @@
       <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="1" t="s">
         <v>38</v>
       </c>
       <c r="H1" s="1" t="s">
@@ -601,10 +607,10 @@
       <c r="E2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F2" s="1">
         <v>0.45</v>
       </c>
-      <c r="G2" s="4">
+      <c r="G2" s="1">
         <v>0.54</v>
       </c>
       <c r="H2" s="1" t="s">
@@ -627,10 +633,10 @@
       <c r="E3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F3" s="1">
         <v>150</v>
       </c>
-      <c r="G3" s="4">
+      <c r="G3" s="1">
         <v>600</v>
       </c>
       <c r="H3" s="1" t="s">
@@ -653,10 +659,10 @@
       <c r="E4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="1">
         <v>4</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G4" s="1">
         <v>17</v>
       </c>
       <c r="H4" s="1" t="s">
@@ -679,10 +685,10 @@
       <c r="E5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="1">
         <v>7</v>
       </c>
-      <c r="G5" s="4">
+      <c r="G5" s="1">
         <v>15</v>
       </c>
       <c r="H5" s="3" t="s">
@@ -705,10 +711,10 @@
       <c r="E6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="1">
         <v>100</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6" s="1">
         <v>1000</v>
       </c>
     </row>
@@ -728,10 +734,10 @@
       <c r="E7" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="1">
         <v>0.3</v>
       </c>
-      <c r="G7" s="4">
+      <c r="G7" s="1">
         <v>1</v>
       </c>
       <c r="H7" s="3" t="s">
@@ -754,10 +760,10 @@
       <c r="E8" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F8" s="4">
+      <c r="F8" s="1">
         <v>0</v>
       </c>
-      <c r="G8" s="4">
+      <c r="G8" s="1">
         <v>0.5</v>
       </c>
       <c r="H8" s="3" t="s">
@@ -777,13 +783,13 @@
       <c r="D9" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E9" s="1">
         <v>0.11</v>
       </c>
-      <c r="F9" s="4">
+      <c r="F9" s="1">
         <v>2</v>
       </c>
-      <c r="G9" s="4">
+      <c r="G9" s="1">
         <v>16</v>
       </c>
       <c r="H9" s="3" t="s">
@@ -803,17 +809,40 @@
       <c r="D10" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E10" s="4">
+      <c r="E10" s="1">
         <v>0.55000000000000004</v>
       </c>
-      <c r="F10" s="4">
+      <c r="F10" s="1">
         <v>27</v>
       </c>
-      <c r="G10" s="4">
+      <c r="G10" s="1">
         <v>22</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="85" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F11" s="1">
+        <v>2</v>
+      </c>
+      <c r="G11" s="1">
+        <v>23</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/data/input_params_range.xlsx
+++ b/data/input_params_range.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geo-checkout-user/Documents/2024_paleosol_PSM_CLP_case_study/paleosol_CLP/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECDDB408-DF17-0846-92FF-41459A7EE762}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16B8DCD6-27A7-D64F-89F8-7FE6E81050DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6520" yWindow="3200" windowWidth="28040" windowHeight="17440" xr2:uid="{C89A10F1-C584-8C4D-85A3-B57BD1FEEBA8}"/>
   </bookViews>
@@ -836,10 +836,10 @@
         <v>33</v>
       </c>
       <c r="F11" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G11" s="1">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>44</v>
